--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\29,06,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB6B91-16EA-4112-BD57-E00C3032F021}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69828B8-6DD2-4191-AB65-BFBA525541FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -124,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +143,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -258,6 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -670,7 +671,7 @@
       <c r="B6" s="2">
         <v>8793</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="12">
         <v>111</v>
       </c>
       <c r="D6" s="2">
@@ -697,7 +698,7 @@
       <c r="B7" s="2">
         <v>8485</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="12">
         <v>182</v>
       </c>
       <c r="D7" s="2">
